--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-references-externes.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-references-externes.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3051" uniqueCount="345">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1039,6 +1039,10 @@
   </si>
   <si>
     <t>ED.thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
   </si>
   <si>
     <t>Act.reference.externalDocument.setId</t>
@@ -10650,7 +10654,7 @@
         <v>74</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>74</v>
+        <v>331</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>74</v>
@@ -10658,10 +10662,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10737,7 +10741,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10757,10 +10761,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10783,7 +10787,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10836,7 +10840,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10856,10 +10860,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10935,7 +10939,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -10955,10 +10959,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -10981,7 +10985,7 @@
         <v>74</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
@@ -11034,7 +11038,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11054,10 +11058,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11080,7 +11084,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -11133,7 +11137,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -11153,10 +11157,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11179,7 +11183,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -11232,7 +11236,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
